--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L15" s="15">
+        <v>100</v>
+      </c>
+      <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="L15" s="15">
-        <v>50</v>
-      </c>
-      <c r="M15" s="15">
-        <v>-25</v>
-      </c>
       <c r="N15" s="15">
-        <v>-78.571428571428</v>
+        <v>-73.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-42.105263157894</v>
+        <v>-31.25</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.095238095238</v>
+        <v>-36</v>
       </c>
       <c r="L16" s="15">
-        <v>8.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.571428571428</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="N16" s="15">
-        <v>-90</v>
+        <v>-89.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F17" s="14">
+        <v>23</v>
+      </c>
+      <c r="G17" s="14">
         <v>24</v>
       </c>
-      <c r="G17" s="14">
-        <v>20</v>
-      </c>
       <c r="H17" s="15">
-        <v>20</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K17" s="15">
-        <v>40.740740740740</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.627906976744</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="15">
-        <v>58.333333333333</v>
+        <v>40</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.222222222222</v>
+        <v>-52.808988764044</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
+      <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-93.333333333333</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="I18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" s="14">
         <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-81.25</v>
+        <v>-68.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M18" s="15">
-        <v>-88</v>
+        <v>-80.769230769230</v>
       </c>
       <c r="N18" s="15">
-        <v>-98.026315789473</v>
+        <v>-97.222222222222</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-70</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J19" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K19" s="15">
-        <v>10.344827586206</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="L19" s="15">
-        <v>3.225806451612</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.030303030303</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>16.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>10</v>
@@ -1125,13 +1125,13 @@
         <v>42.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.076923076923</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>-56.521739130434</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.219653179190</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.529411764705</v>
+        <v>-29.213483146067</v>
       </c>
       <c r="I21" s="17">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J21" s="17">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.807692307692</v>
+        <v>-11.811023622047</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.476635514018</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.260869565217</v>
+        <v>-27.741935483871</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.554817275747</v>
+        <v>-83.908045977011</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>4</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
         <v>14.285714285714</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
         <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.666666666666</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-42.857142857142</v>
+        <v>-46.363636363636</v>
       </c>
       <c r="I24" s="14">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J24" s="14">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.405405405405</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.428571428571</v>
+        <v>-28.143712574850</v>
       </c>
       <c r="M24" s="15">
-        <v>-31.333333333333</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-27.272727272727</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-69.117647058823</v>
+        <v>-69.696969696969</v>
       </c>
       <c r="I25" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K25" s="15">
-        <v>-65.217391304347</v>
+        <v>-65.384615384615</v>
       </c>
       <c r="L25" s="15">
-        <v>-44.827586206896</v>
+        <v>-50</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-52.941176470588</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>-25</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I26" s="14">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>-35.897435897435</v>
+        <v>-33.695652173913</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.076923076923</v>
+        <v>-22.784810126582</v>
       </c>
       <c r="M26" s="15">
-        <v>-56.521739130434</v>
+        <v>-53.435114503816</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="14">
-        <v>5</v>
-      </c>
-      <c r="G27" s="14">
-        <v>6</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-16.666666666666</v>
-      </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
         <v>-50</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="15">
         <v>-100</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
+        <v>5</v>
+      </c>
+      <c r="J15" s="14">
         <v>4</v>
       </c>
-      <c r="J15" s="14">
-        <v>3</v>
-      </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>-73.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-31.25</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-36</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="L16" s="15">
-        <v>33.333333333333</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.387096774193</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.333333333333</v>
+        <v>-88.622754491018</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-55.555555555555</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.166666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="I17" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J17" s="14">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>16.666666666666</v>
+        <v>8.510638297872</v>
       </c>
       <c r="L17" s="15">
-        <v>-25</v>
+        <v>-17.741935483871</v>
       </c>
       <c r="M17" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.808988764044</v>
+        <v>-47.422680412371</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-76.923076923076</v>
+        <v>-30</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>-68.75</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.444444444444</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-80.769230769230</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.222222222222</v>
+        <v>-95.852534562212</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-70</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
         <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.142857142857</v>
+        <v>-40.625</v>
       </c>
       <c r="I19" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J19" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.256410256410</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.256410256410</v>
+        <v>-20</v>
       </c>
       <c r="M19" s="15">
-        <v>-7.894736842105</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.153846153846</v>
+        <v>-46.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
         <v>5</v>
       </c>
-      <c r="G20" s="14">
-        <v>6</v>
-      </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.571428571428</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>-60</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.871794871794</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-43.478260869565</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.213483146067</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I21" s="17">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="J21" s="17">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.811023622047</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.151515151515</v>
+        <v>-12.337662337662</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.741935483871</v>
+        <v>-24.581005586592</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.908045977011</v>
+        <v>-82.976040353089</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>6</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
         <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L23" s="15">
-        <v>14.285714285714</v>
+        <v>75</v>
       </c>
       <c r="M23" s="15">
-        <v>300</v>
+        <v>366.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.166666666666</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F24" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G24" s="14">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>-46.363636363636</v>
+        <v>-42.452830188679</v>
       </c>
       <c r="I24" s="14">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="J24" s="14">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.232558139534</v>
+        <v>-29.533678756476</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.143712574850</v>
+        <v>-30.256410256410</v>
       </c>
       <c r="M24" s="15">
-        <v>-26.829268292682</v>
+        <v>-24.022346368715</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H25" s="15">
-        <v>-69.696969696969</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="K25" s="15">
-        <v>-65.384615384615</v>
+        <v>-63.478260869565</v>
       </c>
       <c r="L25" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>15</v>
+      </c>
+      <c r="D26" s="14">
         <v>11</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>-21.428571428571</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="15">
-        <v>-27.272727272727</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K26" s="15">
-        <v>-33.695652173913</v>
+        <v>-26.213592233009</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.784810126582</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="M26" s="15">
-        <v>-53.435114503816</v>
+        <v>-48.299319727891</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-42.857142857142</v>
-      </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -902,31 +902,31 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I15" s="14">
+        <v>6</v>
+      </c>
+      <c r="J15" s="14">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15">
+        <v>20</v>
+      </c>
+      <c r="L15" s="15">
         <v>50</v>
       </c>
-      <c r="I15" s="14">
-        <v>5</v>
-      </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
-      <c r="K15" s="15">
-        <v>25</v>
-      </c>
-      <c r="L15" s="15">
-        <v>66.666666666666</v>
-      </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>8.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
-        <v>-29.629629629629</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="L16" s="15">
-        <v>35.714285714285</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.648648648648</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.622754491018</v>
+        <v>-89.130434782608</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.75</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="I17" s="14">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K17" s="15">
-        <v>8.510638297872</v>
+        <v>10.909090909090</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.741935483871</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="M17" s="15">
-        <v>50</v>
+        <v>38.636363636363</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.422680412371</v>
+        <v>-46.491228070175</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-30</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
         <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.631578947368</v>
+        <v>-62.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.181818181818</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.857142857142</v>
+        <v>-71.875</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.852534562212</v>
+        <v>-96.498054474708</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-40.625</v>
+        <v>-50</v>
       </c>
       <c r="I19" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J19" s="14">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.893617021276</v>
+        <v>-23.728813559322</v>
       </c>
       <c r="L19" s="15">
-        <v>-20</v>
+        <v>-26.229508196721</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.893617021276</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.666666666666</v>
+        <v>-47.058823529411</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="14">
-        <v>5</v>
-      </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
         <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M20" s="15">
         <v>-60.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-95</v>
+        <v>-95.564516129032</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.692307692307</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.580645161290</v>
+        <v>-27</v>
       </c>
       <c r="I21" s="17">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.764705882352</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.337662337662</v>
+        <v>-20</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.581005586592</v>
+        <v>-24.752475247524</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.976040353089</v>
+        <v>-83.259911894273</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>6</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I23" s="14">
         <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>40</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L23" s="15">
-        <v>75</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M23" s="15">
         <v>366.666666666667</v>
@@ -1265,34 +1265,34 @@
         <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.809523809523</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="F24" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>-42.452830188679</v>
+        <v>-39.215686274509</v>
       </c>
       <c r="I24" s="14">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J24" s="14">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.533678756476</v>
+        <v>-33.185840707964</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.256410256410</v>
+        <v>-31.674208144796</v>
       </c>
       <c r="M24" s="15">
-        <v>-24.022346368715</v>
+        <v>-20.942408376963</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.454545454545</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G25" s="14">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-64.516129032258</v>
+        <v>-50.980392156862</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J25" s="14">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="K25" s="15">
-        <v>-63.478260869565</v>
+        <v>-62.878787878787</v>
       </c>
       <c r="L25" s="15">
-        <v>-53.846153846153</v>
+        <v>-53.773584905660</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>36.363636363636</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>-25</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J26" s="14">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>-26.213592233009</v>
+        <v>-24.347826086956</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.433734939759</v>
+        <v>-16.346153846153</v>
       </c>
       <c r="M26" s="15">
-        <v>-48.299319727891</v>
+        <v>-47.904191616766</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>33.333333333333</v>
+        <v>250</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-62.5</v>
+        <v>-41.176470588235</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.428571428571</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.483870967741</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L16" s="15">
-        <v>11.111111111111</v>
+        <v>26.315789473684</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.130434782608</v>
+        <v>-88.837209302325</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
+        <v>-63.636363636363</v>
+      </c>
+      <c r="F17" s="14">
+        <v>28</v>
+      </c>
+      <c r="G17" s="14">
+        <v>39</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-28.205128205128</v>
+      </c>
+      <c r="I17" s="14">
+        <v>66</v>
+      </c>
+      <c r="J17" s="14">
+        <v>66</v>
+      </c>
+      <c r="K17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>31</v>
-      </c>
-      <c r="G17" s="14">
-        <v>33</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-6.060606060606</v>
-      </c>
-      <c r="I17" s="14">
-        <v>61</v>
-      </c>
-      <c r="J17" s="14">
-        <v>55</v>
-      </c>
-      <c r="K17" s="15">
-        <v>10.909090909090</v>
-      </c>
       <c r="L17" s="15">
-        <v>-17.567567567567</v>
+        <v>-30.526315789473</v>
       </c>
       <c r="M17" s="15">
-        <v>38.636363636363</v>
+        <v>26.923076923076</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.491228070175</v>
+        <v>-49.618320610687</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-62.5</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="M18" s="15">
-        <v>-71.875</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.498054474708</v>
+        <v>-96.699669966996</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J19" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.728813559322</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.229508196721</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.764705882352</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.058823529411</v>
+        <v>-43.157894736842</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>22.222222222222</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.666666666666</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M20" s="15">
-        <v>-60.714285714285</v>
+        <v>-59.375</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.564516129032</v>
+        <v>-95.289855072463</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-51.612903225806</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H21" s="18">
-        <v>-27</v>
+        <v>-22.772277227722</v>
       </c>
       <c r="I21" s="17">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="J21" s="17">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.391304347826</v>
+        <v>-13.658536585365</v>
       </c>
       <c r="L21" s="18">
-        <v>-20</v>
+        <v>-21.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.752475247524</v>
+        <v>-24.680851063829</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.259911894273</v>
+        <v>-82.997118155619</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,34 +1224,34 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>42.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
         <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
         <v>55.555555555555</v>
       </c>
       <c r="M23" s="15">
-        <v>366.666666666667</v>
+        <v>250</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-51.515151515151</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>-39.215686274509</v>
+        <v>-29.473684210526</v>
       </c>
       <c r="I24" s="14">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="J24" s="14">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.185840707964</v>
+        <v>-30.452674897119</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.674208144796</v>
+        <v>-33.201581027668</v>
       </c>
       <c r="M24" s="15">
-        <v>-20.942408376963</v>
+        <v>-20.283018867924</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-58.823529411764</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H25" s="15">
-        <v>-50.980392156862</v>
+        <v>-47.727272727272</v>
       </c>
       <c r="I25" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K25" s="15">
-        <v>-62.878787878787</v>
+        <v>-59.558823529411</v>
       </c>
       <c r="L25" s="15">
-        <v>-53.773584905660</v>
+        <v>-54.918032786885</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-8.333333333333</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.518518518518</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I26" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="K26" s="15">
-        <v>-24.347826086956</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.346153846153</v>
+        <v>-12.5</v>
       </c>
       <c r="M26" s="15">
-        <v>-47.904191616766</v>
+        <v>-48.958333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>11.111111111111</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>4</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-8.333333333333</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.272727272727</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>26.315789473684</v>
+        <v>35</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.936170212766</v>
+        <v>-44.897959183673</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.837209302325</v>
+        <v>-88.412017167382</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-63.636363636363</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.205128205128</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I17" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>1.351351351351</v>
       </c>
       <c r="L17" s="15">
-        <v>-30.526315789473</v>
+        <v>-25.742574257425</v>
       </c>
       <c r="M17" s="15">
-        <v>26.923076923076</v>
+        <v>31.578947368421</v>
       </c>
       <c r="N17" s="15">
-        <v>-49.618320610687</v>
+        <v>-46.043165467625</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-30</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I18" s="14">
         <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>-61.538461538461</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="L18" s="15">
-        <v>-47.368421052631</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="M18" s="15">
-        <v>-72.222222222222</v>
+        <v>-75.609756097561</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.699669966996</v>
+        <v>-97.041420118343</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J19" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.903225806451</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.739130434782</v>
+        <v>-25</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.475409836065</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.157894736842</v>
+        <v>-41.176470588235</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
         <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>8.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.777777777777</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-59.375</v>
+        <v>-60.526315789473</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.289855072463</v>
+        <v>-94.897959183673</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>4.761904761904</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.772277227722</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.658536585365</v>
+        <v>-10.045662100456</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.333333333333</v>
+        <v>-20.242914979757</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.680851063829</v>
+        <v>-23.346303501945</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.997118155619</v>
+        <v>-82.519964507542</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>14</v>
@@ -1248,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>55.555555555555</v>
+        <v>40</v>
       </c>
       <c r="M23" s="15">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
         <v>19</v>
       </c>
-      <c r="D24" s="14">
-        <v>17</v>
-      </c>
       <c r="E24" s="15">
-        <v>11.764705882352</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.473684210526</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I24" s="14">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="J24" s="14">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.452674897119</v>
+        <v>-29.770992366412</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.201581027668</v>
+        <v>-34.982332155477</v>
       </c>
       <c r="M24" s="15">
-        <v>-20.283018867924</v>
+        <v>-22.362869198312</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.727272727272</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K25" s="15">
-        <v>-59.558823529411</v>
+        <v>-60.139860139860</v>
       </c>
       <c r="L25" s="15">
-        <v>-54.918032786885</v>
+        <v>-58.088235294117</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>-26.666666666666</v>
+        <v>-31.25</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.692307692307</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I26" s="14">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J26" s="14">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="K26" s="15">
-        <v>-24.615384615384</v>
+        <v>-26.712328767123</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.5</v>
+        <v>-14.4</v>
       </c>
       <c r="M26" s="15">
-        <v>-48.958333333333</v>
+        <v>-51.363636363636</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>7</v>
+      </c>
+      <c r="G27" s="14">
         <v>5</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>400</v>
-      </c>
-      <c r="F27" s="14">
-        <v>8</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>40</v>
       </c>
       <c r="I27" s="14">
         <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
         <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.333333333333</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -902,22 +902,22 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -926,48 +926,48 @@
         <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-41.176470588235</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>10</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I16" s="14">
         <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="L16" s="15">
-        <v>35</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.897959183673</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.412017167382</v>
+        <v>-88.842975206611</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.5</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
         <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.789473684210</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="I17" s="14">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K17" s="15">
-        <v>1.351351351351</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.742574257425</v>
+        <v>-27.966101694915</v>
       </c>
       <c r="M17" s="15">
-        <v>31.578947368421</v>
+        <v>25</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.043165467625</v>
+        <v>-43.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
         <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.545454545454</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-62.962962962963</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M18" s="15">
-        <v>-75.609756097561</v>
+        <v>-75</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.041420118343</v>
+        <v>-97.027027027027</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I19" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.25</v>
+        <v>2.985074626865</v>
       </c>
       <c r="L19" s="15">
-        <v>-25</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M19" s="15">
-        <v>-7.692307692307</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.176470588235</v>
+        <v>-37.272727272727</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
         <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-60.526315789473</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.897959183673</v>
+        <v>-94.670846394984</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>28.571428571428</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.695652173913</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="I21" s="17">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="J21" s="17">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.045662100456</v>
+        <v>-8.368200836820</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.242914979757</v>
+        <v>-21.223021582733</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.346303501945</v>
+        <v>-23.426573426573</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.519964507542</v>
+        <v>-81.960461285008</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L23" s="15">
-        <v>40</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>180</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.052631578947</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F24" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.777777777777</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I24" s="14">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="J24" s="14">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.770992366412</v>
+        <v>-32.203389830508</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.982332155477</v>
+        <v>-36.305732484076</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.362869198312</v>
+        <v>-25.650557620817</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.153846153846</v>
+        <v>-49.019607843137</v>
       </c>
       <c r="I25" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>-60.139860139860</v>
+        <v>-59.036144578313</v>
       </c>
       <c r="L25" s="15">
-        <v>-58.088235294117</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-31.25</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
+        <v>-32.758620689655</v>
+      </c>
+      <c r="I26" s="14">
+        <v>115</v>
+      </c>
+      <c r="J26" s="14">
+        <v>161</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="L26" s="15">
         <v>-14.814814814814</v>
       </c>
-      <c r="I26" s="14">
-        <v>107</v>
-      </c>
-      <c r="J26" s="14">
-        <v>146</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-26.712328767123</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-14.4</v>
-      </c>
       <c r="M26" s="15">
-        <v>-51.363636363636</v>
+        <v>-54</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,28 +1388,28 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I27" s="14">
         <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
         <v>36.363636363636</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I28" s="14">
+        <v>18</v>
+      </c>
+      <c r="J28" s="14">
         <v>16</v>
       </c>
-      <c r="J28" s="14">
-        <v>15</v>
-      </c>
       <c r="K28" s="15">
-        <v>6.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,7 +1497,7 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
         <v>-88.235294117647</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,7 +1538,7 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
         <v>-86.666666666666</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -895,79 +895,79 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N15" s="15">
-        <v>-44.444444444444</v>
+        <v>-38.888888888888</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.111111111111</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-25</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="L16" s="15">
-        <v>17.391304347826</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-55.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.842975206611</v>
+        <v>-88.537549407114</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.948717948717</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="I17" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.162790697674</v>
+        <v>-1.086956521739</v>
       </c>
       <c r="L17" s="15">
-        <v>-27.966101694915</v>
+        <v>-25.409836065573</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>26.388888888888</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.333333333333</v>
+        <v>-43.827160493827</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-81.818181818181</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
         <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-63.333333333333</v>
+        <v>-65.625</v>
       </c>
       <c r="L18" s="15">
-        <v>-47.619047619047</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-75</v>
+        <v>-78.846153846153</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.027027027027</v>
+        <v>-97.336561743341</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>133.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>40</v>
+        <v>62.5</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J19" s="14">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>2.985074626865</v>
+        <v>-2.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.689655172413</v>
+        <v>-20.652173913043</v>
       </c>
       <c r="M19" s="15">
-        <v>-4.166666666666</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.272727272727</v>
+        <v>-39.166666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,13 +1107,13 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>17</v>
@@ -1125,13 +1125,13 @@
         <v>41.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.166666666666</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M20" s="15">
-        <v>-58.536585365853</v>
+        <v>-61.363636363636</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.670846394984</v>
+        <v>-95.100864553314</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.813953488372</v>
+        <v>4.109589041095</v>
       </c>
       <c r="I21" s="17">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="J21" s="17">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.368200836820</v>
+        <v>-9.727626459143</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.223021582733</v>
+        <v>-22.923588039867</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.426573426573</v>
+        <v>-26.813880126183</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.960461285008</v>
+        <v>-82.397572078907</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
         <v>3</v>
       </c>
-      <c r="E23" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F23" s="14">
-        <v>2</v>
-      </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-71.428571428571</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>-11.764705882352</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>7.142857142857</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>114.285714285714</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-45.454545454545</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H24" s="15">
-        <v>-35.294117647058</v>
+        <v>-32</v>
       </c>
       <c r="I24" s="14">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="J24" s="14">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.203389830508</v>
+        <v>-33.128834355828</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.305732484076</v>
+        <v>-36.443148688046</v>
       </c>
       <c r="M24" s="15">
-        <v>-25.650557620817</v>
+        <v>-26.845637583892</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-52.173913043478</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H25" s="15">
-        <v>-49.019607843137</v>
+        <v>-54.716981132075</v>
       </c>
       <c r="I25" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="K25" s="15">
-        <v>-59.036144578313</v>
+        <v>-60.540540540540</v>
       </c>
       <c r="L25" s="15">
-        <v>-55.263157894736</v>
+        <v>-56.024096385542</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-46.666666666666</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.758620689655</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I26" s="14">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J26" s="14">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="K26" s="15">
-        <v>-28.571428571428</v>
+        <v>-29.444444444444</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.814814814814</v>
+        <v>-13.605442176870</v>
       </c>
       <c r="M26" s="15">
-        <v>-54</v>
+        <v>-53.985507246376</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>20</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L27" s="15">
-        <v>36.363636363636</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
+        <v>17</v>
+      </c>
+      <c r="J28" s="14">
         <v>18</v>
       </c>
-      <c r="J28" s="14">
-        <v>16</v>
-      </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>-18.181818181818</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,35 +1469,35 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N29" s="15">
         <v>-88.235294117647</v>
@@ -1510,35 +1510,35 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
         <v>-86.666666666666</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>150</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N15" s="15">
-        <v>-38.888888888888</v>
+        <v>-45.454545454545</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.621621621621</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.451612903225</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.384615384615</v>
+        <v>-57.971014492753</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.537549407114</v>
+        <v>-89.138576779026</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.621621621621</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J17" s="14">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.086956521739</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.409836065573</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M17" s="15">
-        <v>26.388888888888</v>
+        <v>23.456790123456</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.827160493827</v>
+        <v>-43.820224719101</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
         <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I18" s="14">
         <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-65.625</v>
+        <v>-68.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-54.166666666666</v>
+        <v>-59.259259259259</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.846153846153</v>
+        <v>-81.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.336561743341</v>
+        <v>-97.555555555555</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="15">
-        <v>62.5</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I19" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.666666666666</v>
+        <v>-2.531645569620</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.652173913043</v>
+        <v>-18.947368421052</v>
       </c>
       <c r="M19" s="15">
-        <v>-5.194805194805</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.166666666666</v>
+        <v>-42.962962962963</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>250</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
-        <v>41.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>-34.615384615384</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>-61.363636363636</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.100864553314</v>
+        <v>-94.579945799458</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
         <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>4.109589041095</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="I21" s="17">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="J21" s="17">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.727626459143</v>
+        <v>-10.431654676259</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.923588039867</v>
+        <v>-23.148148148148</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.813880126183</v>
+        <v>-28.034682080924</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.397572078907</v>
+        <v>-82.538569424964</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1230,28 +1230,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L23" s="15">
-        <v>-20</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.935483870967</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>-32</v>
+        <v>-36.036036036036</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="J24" s="14">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.128834355828</v>
+        <v>-32.203389830508</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.443148688046</v>
+        <v>-37.007874015748</v>
       </c>
       <c r="M24" s="15">
-        <v>-26.845637583892</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-73.684210526315</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G25" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-54.716981132075</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J25" s="14">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="K25" s="15">
-        <v>-60.540540540540</v>
+        <v>-59.183673469387</v>
       </c>
       <c r="L25" s="15">
-        <v>-56.024096385542</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.842105263157</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G26" s="14">
         <v>65</v>
       </c>
       <c r="H26" s="15">
-        <v>-38.461538461538</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I26" s="14">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="J26" s="14">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="K26" s="15">
-        <v>-29.444444444444</v>
+        <v>-22.564102564102</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.605442176870</v>
+        <v>-5.031446540880</v>
       </c>
       <c r="M26" s="15">
-        <v>-53.985507246376</v>
+        <v>-48.287671232876</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>20</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>23.076923076923</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
+        <v>20</v>
+      </c>
+      <c r="I28" s="14">
+        <v>20</v>
+      </c>
+      <c r="J28" s="14">
+        <v>20</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="I28" s="14">
-        <v>17</v>
-      </c>
-      <c r="J28" s="14">
-        <v>18</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-5.555555555555</v>
-      </c>
       <c r="L28" s="15">
-        <v>-26.086956521739</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-77.777777777777</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.666666666666</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -902,72 +902,72 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>140</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-45.454545454545</v>
+        <v>-40.909090909090</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.684210526315</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.444444444444</v>
+        <v>-17.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.971014492753</v>
+        <v>-56.578947368421</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.138576779026</v>
+        <v>-88.297872340425</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>8</v>
       </c>
-      <c r="D17" s="14">
-        <v>10</v>
-      </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
         <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.888888888888</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J17" s="14">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.960784313725</v>
+        <v>-3.636363636363</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.242424242424</v>
+        <v>-25.352112676056</v>
       </c>
       <c r="M17" s="15">
-        <v>23.456790123456</v>
+        <v>21.839080459770</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.820224719101</v>
+        <v>-46.464646464646</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-88.888888888888</v>
+        <v>-80</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-68.571428571428</v>
+        <v>-67.567567567567</v>
       </c>
       <c r="L18" s="15">
-        <v>-59.259259259259</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.666666666666</v>
+        <v>-81.25</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.555555555555</v>
+        <v>-97.446808510638</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>29.411764705882</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.531645569620</v>
+        <v>-3.614457831325</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.947368421052</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.962962962963</v>
+        <v>-44.055944055944</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>6</v>
+      </c>
+      <c r="G20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>50</v>
-      </c>
-      <c r="F20" s="14">
-        <v>7</v>
-      </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
       <c r="H20" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>42.857142857142</v>
+        <v>40</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-55.555555555555</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.579945799458</v>
+        <v>-94.642857142857</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.047619047619</v>
+        <v>-15</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.849315068493</v>
+        <v>-17.721518987341</v>
       </c>
       <c r="I21" s="17">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="J21" s="17">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.431654676259</v>
+        <v>-11.073825503355</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.148148148148</v>
+        <v>-23.410404624277</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.034682080924</v>
+        <v>-30.263157894736</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.538569424964</v>
+        <v>-82.473544973545</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-10.526315789473</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.086956521739</v>
+        <v>-28</v>
       </c>
       <c r="M23" s="15">
-        <v>70</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.857142857142</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>-36.036036036036</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="I24" s="14">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="J24" s="14">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.203389830508</v>
+        <v>-30.158730158730</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.007874015748</v>
+        <v>-33.668341708542</v>
       </c>
       <c r="M24" s="15">
-        <v>-25.925925925925</v>
+        <v>-26.462395543175</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.363636363636</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H25" s="15">
-        <v>-58.333333333333</v>
+        <v>-53.731343283582</v>
       </c>
       <c r="I25" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J25" s="14">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="K25" s="15">
-        <v>-59.183673469387</v>
+        <v>-58.095238095238</v>
       </c>
       <c r="L25" s="15">
-        <v>-55.555555555555</v>
+        <v>-53.684210526315</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>-15.384615384615</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J26" s="14">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.564102564102</v>
+        <v>-22.815533980582</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.031446540880</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="M26" s="15">
-        <v>-48.287671232876</v>
+        <v>-48.874598070739</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>21.428571428571</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>41.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>6</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
+        <v>-75</v>
+      </c>
+      <c r="N29" s="15">
         <v>-83.333333333333</v>
-      </c>
-      <c r="N29" s="15">
-        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.5</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,38 +892,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>44.444444444444</v>
+        <v>30</v>
       </c>
       <c r="L15" s="15">
-        <v>116.666666666667</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M15" s="15">
-        <v>116.666666666667</v>
+        <v>30</v>
       </c>
       <c r="N15" s="15">
         <v>-40.909090909090</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.428571428571</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.5</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.578947368421</v>
+        <v>-54.430379746835</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.297872340425</v>
+        <v>-88.311688311688</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F17" s="14">
         <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I17" s="14">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.636363636363</v>
+        <v>-7.258064516129</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.352112676056</v>
+        <v>-23.841059602649</v>
       </c>
       <c r="M17" s="15">
-        <v>21.839080459770</v>
+        <v>25</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.464646464646</v>
+        <v>-44.174757281553</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>-67.567567567567</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="L18" s="15">
-        <v>-57.142857142857</v>
+        <v>-56.25</v>
       </c>
       <c r="M18" s="15">
-        <v>-81.25</v>
+        <v>-79.411764705882</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.446808510638</v>
+        <v>-97.211155378486</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
         <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.263157894736</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.614457831325</v>
+        <v>2.325581395348</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.568627450980</v>
+        <v>-19.266055045871</v>
       </c>
       <c r="M19" s="15">
-        <v>-16.666666666666</v>
+        <v>-16.190476190476</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.055944055944</v>
+        <v>-42.483660130719</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
         <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>40</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="M20" s="15">
-        <v>-57.142857142857</v>
+        <v>-50.980392156862</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.642857142857</v>
+        <v>-94.019138755980</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-15</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.721518987341</v>
+        <v>-11.25</v>
       </c>
       <c r="I21" s="17">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="J21" s="17">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.073825503355</v>
+        <v>-8.777429467084</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.410404624277</v>
+        <v>-21.983914209115</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.263157894736</v>
+        <v>-28.501228501228</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.473544973545</v>
+        <v>-81.981424148606</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-28</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M23" s="15">
-        <v>63.636363636363</v>
+        <v>58.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>4.166666666666</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.310344827586</v>
+        <v>-8.080808080808</v>
       </c>
       <c r="I24" s="14">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J24" s="14">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.158730158730</v>
+        <v>-26.395939086294</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.668341708542</v>
+        <v>-30.288461538461</v>
       </c>
       <c r="M24" s="15">
-        <v>-26.462395543175</v>
+        <v>-23.280423280423</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>9</v>
+      </c>
+      <c r="D25" s="14">
         <v>8</v>
       </c>
-      <c r="D25" s="14">
-        <v>14</v>
-      </c>
       <c r="E25" s="15">
-        <v>-42.857142857142</v>
+        <v>12.5</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H25" s="15">
-        <v>-53.731343283582</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I25" s="14">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="J25" s="14">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.095238095238</v>
+        <v>-55.045871559633</v>
       </c>
       <c r="L25" s="15">
-        <v>-53.684210526315</v>
+        <v>-50.505050505050</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-27.272727272727</v>
+        <v>70</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G26" s="14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.333333333333</v>
+        <v>10.909090909090</v>
       </c>
       <c r="I26" s="14">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J26" s="14">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.815533980582</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.169491525423</v>
+        <v>-9.278350515463</v>
       </c>
       <c r="M26" s="15">
-        <v>-48.874598070739</v>
+        <v>-49.279538904899</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-19.230769230769</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -905,25 +905,25 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L15" s="15">
-        <v>85.714285714285</v>
+        <v>62.5</v>
       </c>
       <c r="M15" s="15">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N15" s="15">
         <v>-40.909090909090</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
         <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>12.5</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
         <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.279069767441</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.430379746835</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.311688311688</v>
+        <v>-89.253731343283</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-35.714285714285</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F17" s="14">
         <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.052631578947</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="I17" s="14">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.258064516129</v>
+        <v>-9.629629629629</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.841059602649</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>20.792079207920</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.174757281553</v>
+        <v>-44.036697247706</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-63.157894736842</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="L18" s="15">
-        <v>-56.25</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.411764705882</v>
+        <v>-78.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.211155378486</v>
+        <v>-97.009345794392</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>5.263157894736</v>
+        <v>68.75</v>
       </c>
       <c r="I19" s="14">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="J19" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K19" s="15">
-        <v>2.325581395348</v>
+        <v>6.593406593406</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.266055045871</v>
+        <v>-14.159292035398</v>
       </c>
       <c r="M19" s="15">
-        <v>-16.190476190476</v>
+        <v>-11.818181818181</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.483660130719</v>
+        <v>-39.751552795031</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>66.666666666666</v>
+        <v>52.941176470588</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.354838709677</v>
+        <v>-18.75</v>
       </c>
       <c r="M20" s="15">
-        <v>-50.980392156862</v>
+        <v>-51.851851851851</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.019138755980</v>
+        <v>-94.130925507900</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
         <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>19.047619047619</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.25</v>
+        <v>-4.819277108433</v>
       </c>
       <c r="I21" s="17">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="J21" s="17">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.777429467084</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.983914209115</v>
+        <v>-22.110552763819</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.501228501228</v>
+        <v>-29.061784897025</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.981424148606</v>
+        <v>-81.976744186046</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,23 +1220,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
+        <v>3</v>
+      </c>
+      <c r="G23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
         <v>19</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>62.5</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.080808080808</v>
+        <v>3.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="J24" s="14">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.395939086294</v>
+        <v>-25.480769230769</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.288461538461</v>
+        <v>-30.022573363431</v>
       </c>
       <c r="M24" s="15">
-        <v>-23.280423280423</v>
+        <v>-23.832923832923</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>12.5</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.307692307692</v>
+        <v>-27.906976744186</v>
       </c>
       <c r="I25" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J25" s="14">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="K25" s="15">
-        <v>-55.045871559633</v>
+        <v>-54.385964912280</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.505050505050</v>
+        <v>-51.173708920187</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>70</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F26" s="14">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>10.909090909090</v>
+        <v>22.448979591836</v>
       </c>
       <c r="I26" s="14">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="J26" s="14">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.518518518518</v>
+        <v>-18.777292576419</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.278350515463</v>
+        <v>-10.144927536231</v>
       </c>
       <c r="M26" s="15">
-        <v>-49.279538904899</v>
+        <v>-49.593495934959</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,13 +1406,13 @@
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>12.5</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>6</v>
-      </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-36.363636363636</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J28" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1494,13 +1494,13 @@
         <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M29" s="15">
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1535,13 +1535,13 @@
         <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M30" s="15">
         <v>-70</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.25</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -902,72 +902,72 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
         <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>62.5</v>
+        <v>30</v>
       </c>
       <c r="M15" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-40.909090909090</v>
+        <v>-43.478260869565</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J16" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K16" s="15">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.404255319148</v>
+        <v>-22</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.142857142857</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.253731343283</v>
+        <v>-88.920454545454</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-36.363636363636</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>-30.232558139534</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="I17" s="14">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.629629629629</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.691358024691</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M17" s="15">
-        <v>20.792079207920</v>
+        <v>24.528301886792</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.036697247706</v>
+        <v>-42.105263157894</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14">
         <v>4</v>
       </c>
-      <c r="G18" s="14">
-        <v>7</v>
-      </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
         <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-58.974358974359</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="L18" s="15">
-        <v>-55.555555555555</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.666666666666</v>
+        <v>-75.641025641025</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.009345794392</v>
+        <v>-96.735395189003</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>9</v>
       </c>
-      <c r="D19" s="14">
-        <v>5</v>
-      </c>
       <c r="E19" s="15">
-        <v>80</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
         <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>68.75</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I19" s="14">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K19" s="15">
-        <v>6.593406593406</v>
+        <v>2</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.159292035398</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.818181818181</v>
+        <v>-15.702479338843</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.751552795031</v>
+        <v>-40.350877192982</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="15">
-        <v>-50</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
         <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>52.941176470588</v>
+        <v>70.588235294117</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.75</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="M20" s="15">
-        <v>-51.851851851851</v>
+        <v>-50.847457627118</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.130925507900</v>
+        <v>-93.829787234042</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
         <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.523809523809</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
         <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.819277108433</v>
+        <v>1.204819277108</v>
       </c>
       <c r="I21" s="17">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="J21" s="17">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.823529411764</v>
+        <v>-7.479224376731</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.110552763819</v>
+        <v>-21.962616822429</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.061784897025</v>
+        <v>-28.632478632478</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.976744186046</v>
+        <v>-81.788440567066</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>200</v>
+        <v>6</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.923076923076</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M23" s="15">
-        <v>58.333333333333</v>
+        <v>64.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.545454545454</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>3.333333333333</v>
+        <v>18.292682926829</v>
       </c>
       <c r="I24" s="14">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="J24" s="14">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.480769230769</v>
+        <v>-23.165137614678</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.022573363431</v>
+        <v>-29.175475687103</v>
       </c>
       <c r="M24" s="15">
-        <v>-23.832923832923</v>
+        <v>-23.690205011389</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-30</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.906976744186</v>
+        <v>-27.659574468085</v>
       </c>
       <c r="I25" s="14">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J25" s="14">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="K25" s="15">
-        <v>-54.385964912280</v>
+        <v>-53.086419753086</v>
       </c>
       <c r="L25" s="15">
-        <v>-51.173708920187</v>
+        <v>-49.107142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>-23.076923076923</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H26" s="15">
-        <v>22.448979591836</v>
+        <v>-6</v>
       </c>
       <c r="I26" s="14">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="J26" s="14">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.777292576419</v>
+        <v>-19.183673469387</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.144927536231</v>
+        <v>-15.744680851063</v>
       </c>
       <c r="M26" s="15">
-        <v>-49.593495934959</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
         <v>5.882352941176</v>
-      </c>
-      <c r="L27" s="15">
-        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-18.181818181818</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I28" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.344827586206</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>-40</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="N29" s="15">
         <v>-84.210526315789</v>
@@ -1538,7 +1538,7 @@
         <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-70</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N30" s="15">
         <v>-82.352941176470</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-120pct.xlsx
+++ b/data/source/weekly/cs-en-us-120pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M15" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-43.478260869565</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
       <c r="E16" s="15">
-        <v>-40</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I16" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>-22</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="L16" s="15">
-        <v>-22</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.666666666666</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.920454545454</v>
+        <v>-87.771739130434</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-20.512820512820</v>
+        <v>18.75</v>
       </c>
       <c r="I17" s="14">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J17" s="14">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.382978723404</v>
+        <v>2.112676056338</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.137931034482</v>
+        <v>-18.539325842696</v>
       </c>
       <c r="M17" s="15">
-        <v>24.528301886792</v>
+        <v>34.259259259259</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.105263157894</v>
+        <v>-39.834024896265</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.282051282051</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.648648648648</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="15">
-        <v>-75.641025641025</v>
+        <v>-75.294117647058</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.735395189003</v>
+        <v>-96.590909090909</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>28.571428571428</v>
+        <v>26.086956521739</v>
       </c>
       <c r="I19" s="14">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J19" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K19" s="15">
-        <v>2</v>
+        <v>2.830188679245</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.073170731707</v>
+        <v>-18.656716417910</v>
       </c>
       <c r="M19" s="15">
-        <v>-15.702479338843</v>
+        <v>-18.045112781954</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.350877192982</v>
+        <v>-38.418079096045</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K20" s="15">
-        <v>70.588235294117</v>
+        <v>63.157894736842</v>
       </c>
       <c r="L20" s="15">
-        <v>-14.705882352941</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>-50.847457627118</v>
+        <v>-51.5625</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.829787234042</v>
+        <v>-93.724696356275</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>1.204819277108</v>
+        <v>24.358974358974</v>
       </c>
       <c r="I21" s="17">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="J21" s="17">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.479224376731</v>
+        <v>-2.925531914893</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.962616822429</v>
+        <v>-18.526785714285</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.632478632478</v>
+        <v>-26.559356136820</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.788440567066</v>
+        <v>-81.078278900985</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>600</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>21.052631578947</v>
+        <v>25</v>
       </c>
       <c r="L23" s="15">
-        <v>-20.689655172413</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="M23" s="15">
-        <v>64.285714285714</v>
+        <v>78.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>-62.5</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>18.292682926829</v>
+        <v>-7.777777777777</v>
       </c>
       <c r="I24" s="14">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="J24" s="14">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.165137614678</v>
+        <v>-25.854700854700</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.175475687103</v>
+        <v>-30.460921843687</v>
       </c>
       <c r="M24" s="15">
-        <v>-23.690205011389</v>
+        <v>-25.536480686695</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.659574468085</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="I25" s="14">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="K25" s="15">
-        <v>-53.086419753086</v>
+        <v>-54.117647058823</v>
       </c>
       <c r="L25" s="15">
-        <v>-49.107142857142</v>
+        <v>-50.423728813559</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>-6</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I26" s="14">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="J26" s="14">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.183673469387</v>
+        <v>-19.615384615384</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.744680851063</v>
+        <v>-14.693877551020</v>
       </c>
       <c r="M26" s="15">
-        <v>-48.571428571428</v>
+        <v>-48.774509803921</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
         <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>5.882352941176</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H28" s="15">
-        <v>-54.545454545454</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.903225806451</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.896551724137</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-76.923076923076</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.210526315789</v>
+        <v>-86.363636363636</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-72.727272727272</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.352941176470</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,14 +1625,14 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>
